--- a/data/trans_dic/KIDMED_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,49</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,82</t>
+          <t>4,93; 15,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,78</t>
+          <t>1,51; 8,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,55</t>
+          <t>4,15; 10,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,26</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 14,81</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>2,34; 14,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,95</t>
+          <t>2,28; 9,4</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,1</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>1,26; 11,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,88</t>
+          <t>1,0; 6,94</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>4,87%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,12</t>
+          <t>2,28; 9,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,77</t>
+          <t>1,95; 8,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,42</t>
+          <t>2,93; 7,89</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,81</t>
+          <t>2,1; 4,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,77</t>
+          <t>1,82; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,88</t>
+          <t>2,26; 4,02</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3883</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5586</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6792</t>
+          <t>0; 3546</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>14078</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1240; 9830</t>
+          <t>5665; 17590</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5980; 18683</t>
+          <t>1499; 8389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9031; 24078</t>
+          <t>8900; 22437</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1284</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2674</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5340</t>
+          <t>0; 3518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4728</t>
+          <t>0; 3865</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6450</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1569; 10320</t>
+          <t>0; 6042</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7137</t>
+          <t>1648; 10031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2521; 12975</t>
+          <t>3201; 13192</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>645</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2732</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>535; 4914</t>
+          <t>0; 4058</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3635</t>
+          <t>556; 5243</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>944; 5768</t>
+          <t>919; 6351</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12779</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2142; 10050</t>
+          <t>3208; 14021</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3414; 15148</t>
+          <t>2372; 10518</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7115; 20674</t>
+          <t>7677; 20716</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>819</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1247</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4398</t>
+          <t>0; 2062</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2588</t>
+          <t>0; 4100</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 4888</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11175; 24904</t>
+          <t>14389; 31658</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16282; 35530</t>
+          <t>11233; 25225</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30492; 54260</t>
+          <t>29442; 52502</t>
         </is>
       </c>
     </row>
